--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -5274,7 +5274,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46232.62438170139</v>
+        <v>46279.143615821755</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>220</v>
@@ -5318,8 +5318,8 @@
       <c r="R68" s="5">
         <v>46286</v>
       </c>
-      <c r="S68" s="7" t="s">
-        <v>32</v>
+      <c r="S68" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -5496,7 +5496,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46232.62438170139</v>
+        <v>46280.16552865741</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>231</v>
@@ -5540,8 +5540,8 @@
       <c r="R72" s="5">
         <v>46287</v>
       </c>
-      <c r="S72" s="7" t="s">
-        <v>32</v>
+      <c r="S72" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -5052,7 +5052,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46274.14175427084</v>
+        <v>46281.25043855324</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>211</v>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46224.887663622685</v>
+        <v>46281.25043436342</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>144</v>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46224.8876609375</v>
+        <v>46281.25043597222</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>144</v>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46224.8876578125</v>
+        <v>46281.250437407405</v>
       </c>
       <c r="E67" s="10" t="s">
         <v>144</v>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46240.822117592594</v>
+        <v>46281.14087030092</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>241</v>
@@ -5762,8 +5762,8 @@
       <c r="R76" s="5">
         <v>46288</v>
       </c>
-      <c r="S76" s="7" t="s">
-        <v>32</v>
+      <c r="S76" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="T76" s="6">
         <v>0</v>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -674,34 +674,34 @@
     <t>Montaje:,Montaje Alabe OT 4375</t>
   </si>
   <si>
+    <t>1216762727729087</t>
+  </si>
+  <si>
+    <t>Revestimiento OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216762727729102</t>
+  </si>
+  <si>
+    <t>1216763050324049</t>
+  </si>
+  <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Revestimiento OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1216762959232537</t>
+  </si>
+  <si>
+    <t>Montaje Alabe OT 4375</t>
+  </si>
+  <si>
+    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Revestimiento OT 4375</t>
+  </si>
+  <si>
+    <t>Montaje:,Montaje Rodete OT 4375</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216762727729087</t>
-  </si>
-  <si>
-    <t>Revestimiento OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216762727729102</t>
-  </si>
-  <si>
-    <t>1216763050324049</t>
-  </si>
-  <si>
-    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Revestimiento OT 4375,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1216762959232537</t>
-  </si>
-  <si>
-    <t>Montaje Alabe OT 4375</t>
-  </si>
-  <si>
-    <t>OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,Revestimiento OT 4375</t>
-  </si>
-  <si>
-    <t>Montaje:,Montaje Rodete OT 4375</t>
   </si>
   <si>
     <t>1216763050389900</t>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46281.25043855324</v>
+        <v>46282.13602961806</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>211</v>
@@ -5096,8 +5096,8 @@
       <c r="R64" s="5">
         <v>46275</v>
       </c>
-      <c r="S64" s="12" t="s">
-        <v>213</v>
+      <c r="S64" s="11" t="s">
+        <v>54</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
@@ -5108,7 +5108,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B65" s="9">
         <v>46224.691826967595</v>
@@ -5151,7 +5151,7 @@
         <v>144</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q65" s="10"/>
       <c r="R65" s="10"/>
@@ -5161,7 +5161,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B66" s="5">
         <v>46224.691831840275</v>
@@ -5204,7 +5204,7 @@
         <v>144</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5214,7 +5214,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B67" s="9">
         <v>46224.69183667824</v>
@@ -5257,7 +5257,7 @@
         <v>144</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5267,7 +5267,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B68" s="5">
         <v>46224.69195275463</v>
@@ -5277,7 +5277,7 @@
         <v>46279.143615821755</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5307,10 +5307,10 @@
         <v>208</v>
       </c>
       <c r="O68" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="P68" s="6" t="s">
         <v>221</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>222</v>
       </c>
       <c r="Q68" s="5">
         <v>46286</v>
@@ -5319,7 +5319,7 @@
         <v>46286</v>
       </c>
       <c r="S68" s="12" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
@@ -5367,7 +5367,7 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O69" s="10" t="s">
         <v>224</v>
@@ -5420,7 +5420,7 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>224</v>
@@ -5473,7 +5473,7 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>229</v>
@@ -5541,7 +5541,7 @@
         <v>46287</v>
       </c>
       <c r="S72" s="12" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>46288</v>
       </c>
       <c r="S76" s="12" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="T76" s="6">
         <v>0</v>
@@ -5940,7 +5940,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46240.822117662035</v>
+        <v>46282.12573053241</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>251</v>
@@ -5984,8 +5984,8 @@
       <c r="R80" s="5">
         <v>46289</v>
       </c>
-      <c r="S80" s="7" t="s">
-        <v>32</v>
+      <c r="S80" s="12" t="s">
+        <v>222</v>
       </c>
       <c r="T80" s="6">
         <v>0</v>

--- a/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
+++ b/data/50001576-  XEMORTIZ FIRST MAJESTIC.xlsx
@@ -1879,7 +1879,7 @@
         <v>46232.537968819444</v>
       </c>
       <c r="D9" s="9">
-        <v>46232.53798356482</v>
+        <v>46284.11321966435</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>42</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="9">
-        <v>46224.727983634264</v>
+        <v>46284.113397187495</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>62</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46224.72969400463</v>
+        <v>46284.11399457176</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>78</v>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46283.16090894676</v>
+        <v>46284.17931957176</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>139</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46274.14413405093</v>
+        <v>46284.16610101852</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>117</v>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46275.14471078703</v>
+        <v>46284.166438113425</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>190</v>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46282.13602961806</v>
+        <v>46284.16791010417</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>212</v>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46279.143615821755</v>
+        <v>46284.168147986114</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>220</v>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46280.16552865741</v>
+        <v>46284.16849015046</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>231</v>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46281.14087030092</v>
+        <v>46284.178164502315</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>241</v>
@@ -5940,7 +5940,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46282.12573053241</v>
+        <v>46284.17871910879</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>251</v>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46232.62438199074</v>
+        <v>46284.178903101856</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>252</v>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46224.888549525465</v>
+        <v>46284.18028267361</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>259</v>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46224.88867554398</v>
+        <v>46284.18039524306</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>275</v>
@@ -6863,7 +6863,7 @@
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46224.88885393519</v>
+        <v>46284.18050556713</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>281</v>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46224.88918993056</v>
+        <v>46284.18071861111</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>287</v>
